--- a/no_match_residual/no_match_residual_2025.xlsx
+++ b/no_match_residual/no_match_residual_2025.xlsx
@@ -583,21 +583,21 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -666,21 +666,21 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -749,21 +749,21 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -832,21 +832,21 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -915,21 +915,21 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -2243,21 +2243,21 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -2326,21 +2326,21 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -2409,21 +2409,21 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -3571,21 +3571,21 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S38" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
@@ -3654,21 +3654,21 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
@@ -3737,21 +3737,21 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -3820,21 +3820,21 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -3903,21 +3903,21 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
@@ -3986,21 +3986,21 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -4069,21 +4069,21 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -4152,21 +4152,21 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S45" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46">
@@ -4235,21 +4235,21 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S46" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47">
@@ -4318,21 +4318,21 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S47" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48">
@@ -4401,21 +4401,21 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
@@ -4484,21 +4484,21 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S49" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
@@ -4567,21 +4567,21 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51">
@@ -4650,21 +4650,21 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
@@ -4733,21 +4733,21 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S52" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
@@ -4816,21 +4816,21 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54">
@@ -4899,21 +4899,21 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55">
@@ -4982,21 +4982,21 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S55" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56">
@@ -5065,21 +5065,21 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57">
@@ -5148,21 +5148,21 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S57" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58">
@@ -5231,21 +5231,21 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S58" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59">
@@ -5314,21 +5314,21 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S59" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60">
@@ -5397,21 +5397,21 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S60" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61">
@@ -5480,21 +5480,21 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S61" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62">
@@ -5563,21 +5563,21 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
@@ -5646,21 +5646,21 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S63" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
@@ -5729,21 +5729,21 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
@@ -5812,21 +5812,21 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S65" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66">
@@ -5895,21 +5895,21 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S66" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67">
@@ -5978,21 +5978,21 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S67" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
@@ -6061,21 +6061,21 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S68" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69">
@@ -6144,21 +6144,21 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70">
@@ -6227,21 +6227,21 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S70" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71">
@@ -6310,21 +6310,21 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72">
@@ -6393,21 +6393,21 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S72" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73">
@@ -6476,21 +6476,21 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S73" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74">
@@ -6559,21 +6559,21 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75">
@@ -6642,21 +6642,21 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S75" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76">
@@ -6725,21 +6725,21 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S76" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77">
@@ -6808,21 +6808,21 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S77" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78">
@@ -6891,21 +6891,21 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S78" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="79">
@@ -6974,21 +6974,21 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S79" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="80">
@@ -7057,21 +7057,21 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S80" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="81">
@@ -7472,21 +7472,21 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86">
@@ -7555,21 +7555,21 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87">
@@ -7638,21 +7638,21 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88">
@@ -7721,21 +7721,21 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89">
@@ -7804,21 +7804,21 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90">
@@ -20669,21 +20669,21 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S244" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="245">
@@ -20752,21 +20752,21 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S245" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="246">
@@ -20835,21 +20835,21 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S246" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="247">
@@ -20918,21 +20918,21 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S247" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="248">
@@ -21001,21 +21001,21 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S248" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="249">
@@ -21084,21 +21084,21 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S249" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="250">
@@ -21167,21 +21167,21 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S250" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="251">
@@ -21250,21 +21250,21 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S251" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="252">
@@ -21333,21 +21333,21 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S252" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="253">
@@ -21416,21 +21416,21 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S253" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="254">
@@ -21665,21 +21665,21 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S256" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="257">
@@ -21748,21 +21748,21 @@
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q257" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S257" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="258">
@@ -21831,21 +21831,21 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q258" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S258" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="259">
@@ -21914,21 +21914,21 @@
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q259" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S259" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="260">
@@ -21997,21 +21997,21 @@
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q260" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S260" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="261">
@@ -22080,21 +22080,21 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q261" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S261" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="262">
@@ -22163,21 +22163,21 @@
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q262" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S262" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="263">
@@ -22246,21 +22246,21 @@
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S263" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="264">
@@ -22329,21 +22329,21 @@
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S264" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="265">
@@ -22412,21 +22412,21 @@
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S265" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="266">
@@ -22495,21 +22495,21 @@
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q266" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S266" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="267">
@@ -22578,21 +22578,21 @@
       </c>
       <c r="P267" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q267" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S267" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="268">
@@ -22661,21 +22661,21 @@
       </c>
       <c r="P268" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q268" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S268" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="269">
@@ -22744,21 +22744,21 @@
       </c>
       <c r="P269" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S269" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="270">
@@ -22993,21 +22993,21 @@
       </c>
       <c r="P272" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S272" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="273">
@@ -23076,21 +23076,21 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S273" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="274">
@@ -23159,21 +23159,21 @@
       </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S274" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="275">
@@ -23242,21 +23242,21 @@
       </c>
       <c r="P275" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S275" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="276">
@@ -23325,21 +23325,21 @@
       </c>
       <c r="P276" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S276" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="277">
@@ -23408,21 +23408,21 @@
       </c>
       <c r="P277" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S277" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="278">
@@ -23491,21 +23491,21 @@
       </c>
       <c r="P278" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S278" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="279">
@@ -23574,21 +23574,21 @@
       </c>
       <c r="P279" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S279" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="280">
@@ -23657,21 +23657,21 @@
       </c>
       <c r="P280" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S280" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="281">
@@ -23740,21 +23740,21 @@
       </c>
       <c r="P281" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S281" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="282">
@@ -23823,21 +23823,21 @@
       </c>
       <c r="P282" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S282" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="283">
@@ -23906,21 +23906,21 @@
       </c>
       <c r="P283" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S283" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="284">
@@ -23989,21 +23989,21 @@
       </c>
       <c r="P284" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S284" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="285">
@@ -24072,21 +24072,21 @@
       </c>
       <c r="P285" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S285" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="286">
@@ -24155,21 +24155,21 @@
       </c>
       <c r="P286" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S286" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="287">
@@ -24238,21 +24238,21 @@
       </c>
       <c r="P287" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S287" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="288">
@@ -24321,21 +24321,21 @@
       </c>
       <c r="P288" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q288" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S288" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="289">
@@ -24404,21 +24404,21 @@
       </c>
       <c r="P289" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q289" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S289" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="290">
@@ -24487,21 +24487,21 @@
       </c>
       <c r="P290" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S290" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="291">
@@ -24570,21 +24570,21 @@
       </c>
       <c r="P291" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S291" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="292">
@@ -24653,21 +24653,21 @@
       </c>
       <c r="P292" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S292" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="293">
@@ -24736,21 +24736,21 @@
       </c>
       <c r="P293" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S293" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="294">
@@ -24819,21 +24819,21 @@
       </c>
       <c r="P294" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q294" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S294" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="295">
@@ -24902,21 +24902,21 @@
       </c>
       <c r="P295" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S295" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="296">
@@ -24985,21 +24985,21 @@
       </c>
       <c r="P296" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S296" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="297">
@@ -25068,21 +25068,21 @@
       </c>
       <c r="P297" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S297" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="298">
@@ -25151,21 +25151,21 @@
       </c>
       <c r="P298" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S298" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="299">
@@ -25234,21 +25234,21 @@
       </c>
       <c r="P299" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q299" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S299" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="300">
@@ -25317,21 +25317,21 @@
       </c>
       <c r="P300" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q300" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S300" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="301">
@@ -25400,21 +25400,21 @@
       </c>
       <c r="P301" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q301" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S301" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="302">
@@ -25483,21 +25483,21 @@
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S302" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="303">
@@ -25566,21 +25566,21 @@
       </c>
       <c r="P303" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S303" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="304">
@@ -25649,21 +25649,21 @@
       </c>
       <c r="P304" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S304" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="305">
@@ -25898,21 +25898,21 @@
       </c>
       <c r="P307" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S307" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="308">
@@ -26064,21 +26064,21 @@
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S309" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="310">
@@ -26230,21 +26230,21 @@
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S311" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="312">
@@ -26313,21 +26313,21 @@
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S312" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="313">
@@ -26396,21 +26396,21 @@
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S313" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="314">
@@ -26479,21 +26479,21 @@
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S314" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="315">
@@ -26562,21 +26562,21 @@
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S315" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="316">
@@ -27309,21 +27309,21 @@
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q324" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S324" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="325">
@@ -27392,21 +27392,21 @@
       </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q325" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S325" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="326">
@@ -31708,21 +31708,21 @@
       </c>
       <c r="P377" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q377" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R377" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S377" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="378">
@@ -31791,21 +31791,21 @@
       </c>
       <c r="P378" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q378" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R378" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S378" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="379">
@@ -31874,21 +31874,21 @@
       </c>
       <c r="P379" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q379" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R379" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S379" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="380">
@@ -32123,21 +32123,21 @@
       </c>
       <c r="P382" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q382" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R382" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S382" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="383">
@@ -32206,21 +32206,21 @@
       </c>
       <c r="P383" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q383" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R383" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S383" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="384">
@@ -32289,21 +32289,21 @@
       </c>
       <c r="P384" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q384" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R384" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S384" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="385">
@@ -32372,21 +32372,21 @@
       </c>
       <c r="P385" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q385" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R385" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S385" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="386">
@@ -32455,21 +32455,21 @@
       </c>
       <c r="P386" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q386" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R386" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S386" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="387">
@@ -32538,21 +32538,21 @@
       </c>
       <c r="P387" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q387" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R387" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S387" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="388">
@@ -32621,21 +32621,21 @@
       </c>
       <c r="P388" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q388" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R388" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S388" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="389">
@@ -32704,21 +32704,21 @@
       </c>
       <c r="P389" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q389" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R389" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S389" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="390">
@@ -32787,21 +32787,21 @@
       </c>
       <c r="P390" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q390" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R390" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S390" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="391">
@@ -32870,21 +32870,21 @@
       </c>
       <c r="P391" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q391" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R391" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S391" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="392">
@@ -32953,21 +32953,21 @@
       </c>
       <c r="P392" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q392" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R392" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S392" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="393">
@@ -33036,21 +33036,21 @@
       </c>
       <c r="P393" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q393" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R393" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S393" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="394">
@@ -33119,21 +33119,21 @@
       </c>
       <c r="P394" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q394" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R394" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S394" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="395">
@@ -33202,21 +33202,21 @@
       </c>
       <c r="P395" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q395" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R395" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S395" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="396">
@@ -33285,21 +33285,21 @@
       </c>
       <c r="P396" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q396" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R396" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S396" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="397">
@@ -33368,21 +33368,21 @@
       </c>
       <c r="P397" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q397" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R397" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S397" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="398">
@@ -33451,21 +33451,21 @@
       </c>
       <c r="P398" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q398" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R398" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S398" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="399">
@@ -33534,21 +33534,21 @@
       </c>
       <c r="P399" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q399" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R399" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S399" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="400">
@@ -33617,21 +33617,21 @@
       </c>
       <c r="P400" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q400" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R400" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S400" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="401">
@@ -33700,21 +33700,21 @@
       </c>
       <c r="P401" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q401" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R401" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S401" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="402">
@@ -33783,21 +33783,21 @@
       </c>
       <c r="P402" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R402" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S402" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="403">
@@ -33866,21 +33866,21 @@
       </c>
       <c r="P403" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q403" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R403" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S403" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="404">
@@ -33949,21 +33949,21 @@
       </c>
       <c r="P404" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q404" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R404" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S404" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="405">
@@ -34032,21 +34032,21 @@
       </c>
       <c r="P405" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q405" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R405" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S405" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="406">
@@ -34115,21 +34115,21 @@
       </c>
       <c r="P406" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q406" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R406" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S406" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="407">
@@ -34198,21 +34198,21 @@
       </c>
       <c r="P407" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q407" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R407" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S407" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="408">
@@ -34281,21 +34281,21 @@
       </c>
       <c r="P408" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q408" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R408" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S408" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="409">
@@ -34364,21 +34364,21 @@
       </c>
       <c r="P409" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q409" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R409" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S409" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="410">
@@ -34449,21 +34449,21 @@
       </c>
       <c r="P410" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q410" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R410" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S410" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="411">
@@ -34532,21 +34532,21 @@
       </c>
       <c r="P411" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q411" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R411" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S411" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="412">
@@ -34615,21 +34615,21 @@
       </c>
       <c r="P412" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q412" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R412" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S412" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="413">
@@ -34698,21 +34698,21 @@
       </c>
       <c r="P413" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q413" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R413" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S413" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="414">
@@ -34781,21 +34781,21 @@
       </c>
       <c r="P414" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q414" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R414" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S414" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="415">
@@ -34864,21 +34864,21 @@
       </c>
       <c r="P415" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q415" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R415" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S415" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="416">
@@ -34947,21 +34947,21 @@
       </c>
       <c r="P416" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q416" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R416" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S416" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="417">
@@ -35030,21 +35030,21 @@
       </c>
       <c r="P417" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q417" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R417" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S417" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="418">
@@ -35113,21 +35113,21 @@
       </c>
       <c r="P418" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q418" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R418" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S418" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="419">
@@ -35279,21 +35279,21 @@
       </c>
       <c r="P420" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q420" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R420" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S420" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="421">
@@ -35364,21 +35364,21 @@
       </c>
       <c r="P421" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q421" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R421" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S421" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="422">
@@ -35447,21 +35447,21 @@
       </c>
       <c r="P422" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q422" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R422" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S422" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="423">
@@ -35530,21 +35530,21 @@
       </c>
       <c r="P423" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q423" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R423" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S423" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="424">
@@ -35611,21 +35611,21 @@
       </c>
       <c r="P424" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q424" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R424" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S424" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="425">
@@ -35775,21 +35775,21 @@
       </c>
       <c r="P426" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q426" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R426" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S426" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="427">
@@ -35856,21 +35856,21 @@
       </c>
       <c r="P427" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q427" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R427" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S427" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="428">
@@ -36231,21 +36231,21 @@
       </c>
       <c r="P432" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R432" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S432" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="433">
@@ -36306,21 +36306,21 @@
       </c>
       <c r="P433" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q433" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R433" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S433" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="434">
@@ -36389,21 +36389,21 @@
       </c>
       <c r="P434" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q434" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R434" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S434" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="435">
@@ -36638,21 +36638,21 @@
       </c>
       <c r="P437" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q437" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R437" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S437" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="438">
@@ -36721,21 +36721,21 @@
       </c>
       <c r="P438" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q438" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R438" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S438" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="439">
@@ -36804,21 +36804,21 @@
       </c>
       <c r="P439" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q439" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R439" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S439" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="440">
@@ -36887,21 +36887,21 @@
       </c>
       <c r="P440" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q440" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R440" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S440" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="441">
@@ -36968,21 +36968,21 @@
       </c>
       <c r="P441" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R441" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S441" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="442">
@@ -37213,21 +37213,21 @@
       </c>
       <c r="P444" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q444" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R444" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S444" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="445">
@@ -37296,21 +37296,21 @@
       </c>
       <c r="P445" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R445" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S445" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="446">
@@ -37379,21 +37379,21 @@
       </c>
       <c r="P446" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R446" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S446" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="447">
@@ -37462,21 +37462,21 @@
       </c>
       <c r="P447" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R447" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S447" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="448">
@@ -37705,21 +37705,21 @@
       </c>
       <c r="P450" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R450" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S450" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="451">
@@ -37950,21 +37950,21 @@
       </c>
       <c r="P453" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q453" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R453" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S453" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="454">
@@ -38033,21 +38033,21 @@
       </c>
       <c r="P454" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q454" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R454" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S454" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="455">
@@ -38116,21 +38116,21 @@
       </c>
       <c r="P455" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q455" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R455" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S455" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="456">
@@ -38197,21 +38197,21 @@
       </c>
       <c r="P456" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q456" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R456" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S456" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="457">
@@ -38280,21 +38280,21 @@
       </c>
       <c r="P457" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q457" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R457" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S457" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="458">
@@ -38363,21 +38363,21 @@
       </c>
       <c r="P458" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q458" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R458" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S458" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="459">
@@ -38444,21 +38444,21 @@
       </c>
       <c r="P459" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q459" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R459" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S459" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="460">
@@ -38527,21 +38527,21 @@
       </c>
       <c r="P460" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q460" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R460" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S460" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="461">
@@ -38608,21 +38608,21 @@
       </c>
       <c r="P461" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q461" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R461" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S461" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="462">
@@ -38689,21 +38689,21 @@
       </c>
       <c r="P462" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q462" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R462" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S462" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="463">
@@ -38770,21 +38770,21 @@
       </c>
       <c r="P463" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q463" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R463" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S463" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="464">
@@ -38851,21 +38851,21 @@
       </c>
       <c r="P464" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q464" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R464" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S464" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="465">
@@ -38932,21 +38932,21 @@
       </c>
       <c r="P465" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q465" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R465" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S465" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="466">
@@ -39013,21 +39013,21 @@
       </c>
       <c r="P466" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q466" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R466" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S466" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="467">
@@ -39094,21 +39094,21 @@
       </c>
       <c r="P467" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q467" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R467" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S467" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="468">
@@ -39177,21 +39177,21 @@
       </c>
       <c r="P468" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q468" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R468" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S468" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="469">
@@ -39256,21 +39256,21 @@
       </c>
       <c r="P469" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q469" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R469" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S469" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="470">
@@ -39335,21 +39335,21 @@
       </c>
       <c r="P470" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q470" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R470" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S470" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="471">
@@ -39497,21 +39497,21 @@
       </c>
       <c r="P472" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q472" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R472" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S472" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="473">
@@ -39578,21 +39578,21 @@
       </c>
       <c r="P473" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q473" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R473" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S473" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="474">
@@ -39659,21 +39659,21 @@
       </c>
       <c r="P474" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q474" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R474" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S474" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="475">
@@ -39742,21 +39742,21 @@
       </c>
       <c r="P475" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q475" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R475" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S475" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="476">
@@ -39825,21 +39825,21 @@
       </c>
       <c r="P476" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>99000000</t>
         </is>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R476" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos Post-Mortem</t>
         </is>
       </c>
       <c r="S476" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="477">
@@ -39908,21 +39908,21 @@
       </c>
       <c r="P477" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q477" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R477" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S477" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="478">
@@ -39991,21 +39991,21 @@
       </c>
       <c r="P478" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q478" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R478" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S478" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="479">
@@ -40074,21 +40074,21 @@
       </c>
       <c r="P479" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q479" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R479" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S479" t="n">
-        <v>92</v>
+        <v>40</v>
       </c>
     </row>
     <row r="480">
@@ -40157,21 +40157,21 @@
       </c>
       <c r="P480" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q480" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R480" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S480" t="n">
-        <v>92</v>
+        <v>40</v>
       </c>
     </row>
     <row r="481">
@@ -40240,21 +40240,21 @@
       </c>
       <c r="P481" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q481" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R481" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S481" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="482">
@@ -40323,21 +40323,21 @@
       </c>
       <c r="P482" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q482" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R482" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S482" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="483">
@@ -40406,21 +40406,21 @@
       </c>
       <c r="P483" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q483" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R483" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S483" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="484">
@@ -40489,21 +40489,21 @@
       </c>
       <c r="P484" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q484" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R484" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S484" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="485">
@@ -40572,21 +40572,21 @@
       </c>
       <c r="P485" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q485" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R485" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S485" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="486">
@@ -40655,21 +40655,21 @@
       </c>
       <c r="P486" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q486" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R486" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S486" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="487">
@@ -40738,21 +40738,21 @@
       </c>
       <c r="P487" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q487" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R487" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S487" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="488">
@@ -40821,21 +40821,21 @@
       </c>
       <c r="P488" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q488" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R488" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S488" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="489">
@@ -40987,21 +40987,21 @@
       </c>
       <c r="P490" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q490" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R490" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S490" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="491">
@@ -41066,21 +41066,21 @@
       </c>
       <c r="P491" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q491" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R491" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S491" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="492">
@@ -41145,21 +41145,21 @@
       </c>
       <c r="P492" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q492" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R492" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S492" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="493">
@@ -41224,21 +41224,21 @@
       </c>
       <c r="P493" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q493" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R493" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S493" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="494">
@@ -41303,21 +41303,21 @@
       </c>
       <c r="P494" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q494" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R494" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S494" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="495">
@@ -41382,21 +41382,21 @@
       </c>
       <c r="P495" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q495" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R495" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S495" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="496">
@@ -41461,21 +41461,21 @@
       </c>
       <c r="P496" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q496" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R496" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S496" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="497">
@@ -41793,21 +41793,21 @@
       </c>
       <c r="P500" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q500" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R500" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S500" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="501">
@@ -41876,21 +41876,21 @@
       </c>
       <c r="P501" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q501" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R501" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S501" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="502">
@@ -42040,21 +42040,21 @@
       </c>
       <c r="P503" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q503" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R503" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S503" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="504">
@@ -42121,21 +42121,21 @@
       </c>
       <c r="P504" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q504" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R504" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S504" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="505">
@@ -42202,21 +42202,21 @@
       </c>
       <c r="P505" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q505" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R505" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S505" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="506">
@@ -42283,21 +42283,21 @@
       </c>
       <c r="P506" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q506" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R506" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S506" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="507">
@@ -42362,21 +42362,21 @@
       </c>
       <c r="P507" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>51000000</t>
         </is>
       </c>
       <c r="Q507" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R507" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Asistencia sanitaria</t>
         </is>
       </c>
       <c r="S507" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="508">
@@ -43097,21 +43097,21 @@
       </c>
       <c r="P516" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q516" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R516" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S516" t="n">
-        <v>92</v>
+        <v>40</v>
       </c>
     </row>
     <row r="517">
@@ -43583,21 +43583,21 @@
       </c>
       <c r="P522" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q522" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R522" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S522" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="523">
@@ -43664,21 +43664,21 @@
       </c>
       <c r="P523" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q523" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R523" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S523" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="524">
@@ -44231,21 +44231,21 @@
       </c>
       <c r="P530" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q530" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R530" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S530" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="531">
@@ -44393,21 +44393,21 @@
       </c>
       <c r="P532" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q532" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R532" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S532" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="533">
@@ -44474,21 +44474,21 @@
       </c>
       <c r="P533" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q533" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R533" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S533" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="534">
@@ -44555,21 +44555,21 @@
       </c>
       <c r="P534" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q534" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R534" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S534" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="535">
@@ -45932,21 +45932,21 @@
       </c>
       <c r="P551" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q551" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R551" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S551" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="552">
@@ -46013,21 +46013,21 @@
       </c>
       <c r="P552" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q552" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R552" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S552" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="553">
@@ -46094,21 +46094,21 @@
       </c>
       <c r="P553" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q553" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R553" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S553" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="554">
@@ -46580,21 +46580,21 @@
       </c>
       <c r="P559" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q559" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R559" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S559" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="560">
@@ -46661,21 +46661,21 @@
       </c>
       <c r="P560" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q560" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R560" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S560" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="561">
@@ -46742,21 +46742,21 @@
       </c>
       <c r="P561" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q561" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R561" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S561" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="562">
@@ -48524,21 +48524,21 @@
       </c>
       <c r="P583" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q583" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R583" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S583" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="584">
@@ -48605,21 +48605,21 @@
       </c>
       <c r="P584" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q584" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R584" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S584" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="585">
@@ -48686,21 +48686,21 @@
       </c>
       <c r="P585" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q585" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R585" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S585" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="586">
@@ -49010,21 +49010,21 @@
       </c>
       <c r="P589" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q589" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R589" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S589" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="590">
@@ -50063,21 +50063,21 @@
       </c>
       <c r="P602" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q602" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R602" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S602" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="603">
@@ -50144,21 +50144,21 @@
       </c>
       <c r="P603" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q603" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R603" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S603" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="604">
@@ -50225,21 +50225,21 @@
       </c>
       <c r="P604" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q604" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R604" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S604" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="605">
@@ -50630,21 +50630,21 @@
       </c>
       <c r="P609" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q609" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R609" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S609" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="610">
@@ -50711,21 +50711,21 @@
       </c>
       <c r="P610" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q610" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R610" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S610" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="611">
@@ -50792,21 +50792,21 @@
       </c>
       <c r="P611" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q611" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R611" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S611" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="612">
@@ -51278,21 +51278,21 @@
       </c>
       <c r="P617" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q617" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R617" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S617" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="618">
@@ -52898,21 +52898,21 @@
       </c>
       <c r="P637" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q637" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R637" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S637" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="638">
@@ -54518,21 +54518,21 @@
       </c>
       <c r="P657" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q657" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R657" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S657" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="658">
@@ -55814,21 +55814,21 @@
       </c>
       <c r="P673" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q673" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R673" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S673" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="674">
@@ -55895,21 +55895,21 @@
       </c>
       <c r="P674" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q674" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R674" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S674" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="675">
@@ -57353,21 +57353,21 @@
       </c>
       <c r="P692" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q692" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R692" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S692" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="693">
@@ -57434,21 +57434,21 @@
       </c>
       <c r="P693" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q693" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R693" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S693" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="694">
@@ -57596,21 +57596,21 @@
       </c>
       <c r="P695" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q695" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R695" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S695" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="696">
@@ -59135,21 +59135,21 @@
       </c>
       <c r="P714" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q714" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R714" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S714" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="715">
@@ -60431,21 +60431,21 @@
       </c>
       <c r="P730" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q730" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R730" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S730" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="731">
@@ -60512,21 +60512,21 @@
       </c>
       <c r="P731" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q731" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R731" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S731" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="732">
@@ -60836,21 +60836,21 @@
       </c>
       <c r="P735" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q735" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R735" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S735" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="736">
@@ -60917,21 +60917,21 @@
       </c>
       <c r="P736" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q736" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R736" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S736" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="737">
@@ -60998,21 +60998,21 @@
       </c>
       <c r="P737" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q737" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R737" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S737" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="738">
@@ -63347,21 +63347,21 @@
       </c>
       <c r="P766" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q766" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R766" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S766" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="767">
@@ -64078,21 +64078,21 @@
       </c>
       <c r="P775" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q775" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R775" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S775" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="776">
@@ -64159,21 +64159,21 @@
       </c>
       <c r="P776" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>47000000</t>
         </is>
       </c>
       <c r="Q776" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R776" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Productos de limpieza/higiene</t>
         </is>
       </c>
       <c r="S776" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="777">
@@ -64406,21 +64406,21 @@
       </c>
       <c r="P779" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q779" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R779" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S779" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="780">
@@ -64487,21 +64487,21 @@
       </c>
       <c r="P780" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q780" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R780" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S780" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="781">
@@ -64568,21 +64568,21 @@
       </c>
       <c r="P781" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q781" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R781" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S781" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="782">
@@ -64730,21 +64730,21 @@
       </c>
       <c r="P783" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q783" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R783" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S783" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="784">
@@ -64811,21 +64811,21 @@
       </c>
       <c r="P784" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>53000000</t>
         </is>
       </c>
       <c r="Q784" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R784" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Belleza/cuidado personal/higiene</t>
         </is>
       </c>
       <c r="S784" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="785">
@@ -65054,21 +65054,21 @@
       </c>
       <c r="P787" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q787" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R787" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S787" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="788">
@@ -65135,21 +65135,21 @@
       </c>
       <c r="P788" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q788" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R788" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S788" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="789">
@@ -65216,21 +65216,21 @@
       </c>
       <c r="P789" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q789" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R789" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S789" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
     <row r="790">
@@ -65297,21 +65297,21 @@
       </c>
       <c r="P790" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>50000000</t>
         </is>
       </c>
       <c r="Q790" t="inlineStr">
         <is>
-          <t>NO_MATCH</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="R790" t="inlineStr">
         <is>
-          <t>Sin coincidencia válida</t>
+          <t>Alimentos/Bebidas</t>
         </is>
       </c>
       <c r="S790" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
